--- a/Boltonia_all_metadata_20250815.xlsx
+++ b/Boltonia_all_metadata_20250815.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/wen-hsi_kuo_wustl_edu/Documents/MOBOT/MOBOT_Boltonia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B7DBDCD68F79A8536E3CA493EA7BD272FAC4D4D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAA96D78-83D9-7A40-A79F-CB89B65E7A7D}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_B7DBDCD68F79A8536E3CA493EA7BD272FAC4D4D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3513A851-CFEC-9548-9E92-1E4108EE61D4}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="34320" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2273,7 +2273,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2285,6 +2285,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2310,12 +2317,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2624,6 +2633,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33815,7 +33830,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>729</v>
       </c>
@@ -33832,7 +33847,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>731</v>
       </c>
@@ -33855,7 +33870,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>732</v>
       </c>
@@ -33878,7 +33893,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>733</v>
       </c>
@@ -33901,7 +33916,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>734</v>
       </c>
@@ -33924,7 +33939,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>736</v>
       </c>
@@ -33947,7 +33962,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>737</v>
       </c>
@@ -33970,7 +33985,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>739</v>
       </c>
@@ -33987,7 +34002,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>741</v>
       </c>
@@ -34004,7 +34019,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>742</v>
       </c>
@@ -34027,7 +34042,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>743</v>
       </c>
@@ -34050,30 +34065,31 @@
         <v>740</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A492" t="s">
+    <row r="492" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A492" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B492" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="C492" t="s">
+      <c r="C492" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="D492" t="b">
-        <v>1</v>
-      </c>
-      <c r="E492" t="b">
-        <v>1</v>
-      </c>
-      <c r="F492">
+      <c r="D492" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E492" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F492" s="3">
         <v>491</v>
       </c>
-      <c r="G492" t="s">
+      <c r="G492" s="3" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="T492" s="4"/>
+    </row>
+    <row r="493" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>746</v>
       </c>
@@ -34096,7 +34112,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>747</v>
       </c>
